--- a/indicadores/ARG-M_out.xlsx
+++ b/indicadores/ARG-M_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Importaciones argentinas de bienes</t>
+    <t xml:space="preserve">Importaciones de bienes</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -74,6 +74,12 @@
     <t xml:space="preserve">td1coef | easter[1]</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -107,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">21/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">fleiva</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -2268,9 +2274,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -2281,7 +2291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -2295,12 +2305,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.672850464658403</v>
+        <v>0.674660126747741</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -2311,7 +2321,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -2339,7 +2349,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -2353,12 +2363,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.423033821239139</v>
+        <v>0.424667240232745</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -2381,7 +2391,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -2395,7 +2405,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -2409,7 +2419,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -2423,12 +2433,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.0128955563945719</v>
+        <v>0.0217637630747699</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -2439,7 +2449,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -2453,12 +2463,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.000000565222604197002</v>
+        <v>0.000000438803399859245</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -2601,10 +2611,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -2617,10 +2627,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -2644,66 +2654,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>385.75274</v>
@@ -2756,7 +2766,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>226.159215</v>
@@ -2813,7 +2823,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>302.887158</v>
@@ -2870,7 +2880,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>276.457304</v>
@@ -2927,7 +2937,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>302.133491</v>
@@ -2984,7 +2994,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>267.684292</v>
@@ -3041,7 +3051,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>313.410346</v>
@@ -3098,7 +3108,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>312.275644</v>
@@ -3155,7 +3165,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>326.249139</v>
@@ -3212,7 +3222,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>424.849874</v>
@@ -3269,7 +3279,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>439.175049</v>
@@ -3326,7 +3336,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>499.63075</v>
@@ -3383,7 +3393,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>492.608171</v>
@@ -3442,7 +3452,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>400.271263</v>
@@ -3501,7 +3511,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>407.690465</v>
@@ -3560,7 +3570,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>614.437466</v>
@@ -3619,7 +3629,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>522.076633</v>
@@ -3678,7 +3688,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>606.455566</v>
@@ -3737,7 +3747,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>748.355735</v>
@@ -3796,7 +3806,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>759.651026</v>
@@ -3855,7 +3865,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>768.24893</v>
@@ -3914,7 +3924,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>936.879785</v>
@@ -3973,7 +3983,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1054.902065</v>
@@ -4032,7 +4042,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>963.693829</v>
@@ -4091,7 +4101,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>902.946207</v>
@@ -4150,7 +4160,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>914.187817</v>
@@ -4209,7 +4219,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1070.337821</v>
@@ -4268,7 +4278,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1186.042169</v>
@@ -4327,7 +4337,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1110.860199</v>
@@ -4386,7 +4396,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1284.734088</v>
@@ -4445,7 +4455,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1459.96013</v>
@@ -4504,7 +4514,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1429.65203</v>
@@ -4563,7 +4573,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1465.142073</v>
@@ -4622,7 +4632,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1516.816844</v>
@@ -4681,7 +4691,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1273.692829</v>
@@ -4740,7 +4750,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1257.381961</v>
@@ -4799,7 +4809,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1038.647448</v>
@@ -4858,7 +4868,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>897.605584</v>
@@ -4917,7 +4927,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1322.928657</v>
@@ -4976,7 +4986,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1206.81051</v>
@@ -5035,7 +5045,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1253.398408</v>
@@ -5094,7 +5104,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1410.186221</v>
@@ -5153,7 +5163,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1559.202869</v>
@@ -5212,7 +5222,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1538.31554</v>
@@ -5271,7 +5281,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1562.630385</v>
@@ -5330,7 +5340,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1570.284496</v>
@@ -5389,7 +5399,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1757.792572</v>
@@ -5448,7 +5458,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>1665.710237</v>
@@ -5507,7 +5517,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>1578.238036</v>
@@ -5566,7 +5576,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>1487.035885</v>
@@ -5625,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1849.848279</v>
@@ -5684,7 +5694,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>1751.819589</v>
@@ -5743,7 +5753,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>1740.954586</v>
@@ -5802,7 +5812,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>1835.794898</v>
@@ -5861,7 +5871,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>1775.966983</v>
@@ -5920,7 +5930,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>2102.829972</v>
@@ -5979,7 +5989,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>1766.01408</v>
@@ -6038,7 +6048,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>1840.003546</v>
@@ -6097,7 +6107,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>1891.852982</v>
@@ -6156,7 +6166,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>1969.896542</v>
@@ -6215,7 +6225,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>1717.910739</v>
@@ -6274,7 +6284,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>1629.544245</v>
@@ -6333,7 +6343,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>1890.613932</v>
@@ -6392,7 +6402,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>1485.177409</v>
@@ -6451,7 +6461,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>1721.813152</v>
@@ -6510,7 +6520,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>1573.118779</v>
@@ -6569,7 +6579,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>1518.781747</v>
@@ -6628,7 +6638,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>1743.831589</v>
@@ -6687,7 +6697,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>1654.549873</v>
@@ -6746,7 +6756,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>1752.375214</v>
@@ -6805,7 +6815,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>1833.026093</v>
@@ -6864,7 +6874,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>1600.93972</v>
@@ -6923,7 +6933,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>1681.946086</v>
@@ -6982,7 +6992,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>1522.092476</v>
@@ -7041,7 +7051,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>1781.66975</v>
@@ -7100,7 +7110,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>1812.935182</v>
@@ -7159,7 +7169,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>1916.198684</v>
@@ -7218,7 +7228,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>1996.430468</v>
@@ -7277,7 +7287,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>2291.016833</v>
@@ -7336,7 +7346,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>2307.531306</v>
@@ -7395,7 +7405,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>1980.870151</v>
@@ -7454,7 +7464,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>2294.085075</v>
@@ -7513,7 +7523,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>2098.768905</v>
@@ -7572,7 +7582,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>2078.263976</v>
@@ -7631,7 +7641,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>2333.374522</v>
@@ -7690,7 +7700,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>2026.635464</v>
@@ -7749,7 +7759,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>2133.055331</v>
@@ -7808,7 +7818,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>2529.043342</v>
@@ -7867,7 +7877,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>2543.884835</v>
@@ -7926,7 +7936,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>2446.750637</v>
@@ -7985,7 +7995,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>2733.556414</v>
@@ -8044,7 +8054,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>2693.938373</v>
@@ -8103,7 +8113,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>2766.845686</v>
@@ -8162,7 +8172,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>2836.165533</v>
@@ -8221,7 +8231,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>2799.478241</v>
@@ -8280,7 +8290,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>2607.45558</v>
@@ -8339,7 +8349,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>2558.320938</v>
@@ -8398,7 +8408,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>2282.81215</v>
@@ -8457,7 +8467,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>2693.948937</v>
@@ -8516,7 +8526,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>2739.397399</v>
@@ -8575,7 +8585,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>2625.797703</v>
@@ -8634,7 +8644,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>2823.103117</v>
@@ -8693,7 +8703,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>3027.288463</v>
@@ -8752,7 +8762,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>2740.494494</v>
@@ -8811,7 +8821,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>2660.692638</v>
@@ -8870,7 +8880,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>2591.191333</v>
@@ -8929,7 +8939,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>2456.459198</v>
@@ -8988,7 +8998,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>2177.853901</v>
@@ -9047,7 +9057,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>1906.339612</v>
@@ -9106,7 +9116,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>1855.728419</v>
@@ -9165,7 +9175,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>2078.156161</v>
@@ -9224,7 +9234,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>1873.381965</v>
@@ -9283,7 +9293,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>1930.700242</v>
@@ -9342,7 +9352,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>2212.477304</v>
@@ -9401,7 +9411,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>2278.15093</v>
@@ -9460,7 +9470,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>2330.824814</v>
@@ -9519,7 +9529,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>2233.969426</v>
@@ -9578,7 +9588,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>2213.08487</v>
@@ -9637,7 +9647,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>2290.06047</v>
@@ -9696,7 +9706,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>2305.283163</v>
@@ -9755,7 +9765,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>1852.193641</v>
@@ -9814,7 +9824,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>1907.761751</v>
@@ -9873,7 +9883,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>2116.315833</v>
@@ -9932,7 +9942,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>1905.387148</v>
@@ -9991,7 +10001,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>2215.13106</v>
@@ -10050,7 +10060,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>2178.239002</v>
@@ -10109,7 +10119,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>2201.590618</v>
@@ -10168,7 +10178,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>2319.562385</v>
@@ -10227,7 +10237,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>2083.755144</v>
@@ -10286,7 +10296,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>2251.365851</v>
@@ -10345,7 +10355,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>2184.621858</v>
@@ -10404,7 +10414,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>2064.560923</v>
@@ -10463,7 +10473,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>1954.05538</v>
@@ -10522,7 +10532,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>1753.888</v>
@@ -10581,7 +10591,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>2034.960501</v>
@@ -10640,7 +10650,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>1917.986285</v>
@@ -10699,7 +10709,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>2080.779547</v>
@@ -10758,7 +10768,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>1777.331684</v>
@@ -10817,7 +10827,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>1769.34889</v>
@@ -10876,7 +10886,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>1822.26093</v>
@@ -10935,7 +10945,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>1431.492715</v>
@@ -10994,7 +11004,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>1511.836087</v>
@@ -11053,7 +11063,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>1333.733876</v>
@@ -11112,7 +11122,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>931.90529</v>
@@ -11171,7 +11181,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>850.579913</v>
@@ -11230,7 +11240,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>627.759578</v>
@@ -11289,7 +11299,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>592.89003</v>
@@ -11348,7 +11358,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>612.000097</v>
@@ -11407,7 +11417,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>861.772801</v>
@@ -11466,7 +11476,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>682.741867</v>
@@ -11525,7 +11535,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>811.047619</v>
@@ -11584,7 +11594,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>762.017442</v>
@@ -11643,7 +11653,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>719.03624</v>
@@ -11702,7 +11712,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>875.887994</v>
@@ -11761,7 +11771,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>808.925851</v>
@@ -11820,7 +11830,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>784.885921</v>
@@ -11879,7 +11889,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>798.965113</v>
@@ -11938,7 +11948,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>776.897236</v>
@@ -11997,7 +12007,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>933.671292</v>
@@ -12056,7 +12066,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>1109.900313</v>
@@ -12115,7 +12125,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>1085.073495</v>
@@ -12174,7 +12184,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>1149.080471</v>
@@ -12233,7 +12243,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>1259.782508</v>
@@ -12292,7 +12302,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>1135.068814</v>
@@ -12351,7 +12361,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>1318.22355</v>
@@ -12410,7 +12420,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>1439.599106</v>
@@ -12469,7 +12479,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>1336.225802</v>
@@ -12528,7 +12538,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>1508.286436</v>
@@ -12587,7 +12597,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>1608.575067</v>
@@ -12646,7 +12656,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>1363.731431</v>
@@ -12705,7 +12715,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>1690.058163</v>
@@ -12764,7 +12774,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>1650.876869</v>
@@ -12823,7 +12833,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B174" s="2" t="n">
         <v>1792.15734</v>
@@ -12882,7 +12892,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B175" s="2" t="n">
         <v>2039.339799</v>
@@ -12941,7 +12951,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>1969.827469</v>
@@ -13000,7 +13010,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>2031.629332</v>
@@ -13059,7 +13069,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>2025.221298</v>
@@ -13118,7 +13128,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>1972.50071</v>
@@ -13177,7 +13187,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>2192.617922</v>
@@ -13236,7 +13246,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>2108.745995</v>
@@ -13295,7 +13305,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>1901.01315326</v>
@@ -13354,7 +13364,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>1867.28695072</v>
@@ -13413,7 +13423,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>2197.56781069</v>
@@ -13472,7 +13482,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>2379.91431089</v>
@@ -13531,7 +13541,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>2475.96668188</v>
@@ -13590,7 +13600,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>2723.61559605</v>
@@ -13649,7 +13659,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>2349.03494825</v>
@@ -13708,7 +13718,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>2625.66841328</v>
@@ -13767,7 +13777,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>2468.08392313</v>
@@ -13826,7 +13836,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>2502.67688541</v>
@@ -13885,7 +13895,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>2701.12671541</v>
@@ -13944,7 +13954,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>2494.93414456</v>
@@ -14003,7 +14013,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>2323.63815691</v>
@@ -14062,7 +14072,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>2326.03863689</v>
@@ -14121,7 +14131,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>2722.10569931</v>
@@ -14180,7 +14190,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>2545.46705789</v>
@@ -14239,7 +14249,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>2825.92754639</v>
@@ -14298,7 +14308,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>2859.17932532</v>
@@ -14357,7 +14367,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>2852.36632267</v>
@@ -14416,7 +14426,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>3280.79358685</v>
@@ -14475,7 +14485,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>3169.427296</v>
@@ -14534,7 +14544,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>3255.11398568</v>
@@ -14593,7 +14603,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>3237.23025431</v>
@@ -14652,7 +14662,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>2756.39460339</v>
@@ -14711,7 +14721,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>2951.04225528</v>
@@ -14770,7 +14780,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>2790.78121339</v>
@@ -14829,7 +14839,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>3422.11019552</v>
@@ -14888,7 +14898,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>3060.8982462</v>
@@ -14947,7 +14957,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>3542.11578779</v>
@@ -15006,7 +15016,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>3578.93874324</v>
@@ -15065,7 +15075,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>4125.80859236</v>
@@ -15124,7 +15134,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>4606.39625312</v>
@@ -15183,7 +15193,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>3963.06097141</v>
@@ -15242,7 +15252,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>4400.47768436</v>
@@ -15301,7 +15311,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>4384.49982718</v>
@@ -15360,7 +15370,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>3881.33362587</v>
@@ -15419,7 +15429,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>4478.52645426</v>
@@ -15478,7 +15488,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>4209.77681544</v>
@@ -15537,7 +15547,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>4163.39683265</v>
@@ -15596,7 +15606,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>4929.57344426</v>
@@ -15655,7 +15665,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>5200.4647047</v>
@@ -15714,7 +15724,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>5195.99173964</v>
@@ -15773,7 +15783,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>6046.82699384</v>
@@ -15832,7 +15842,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>5158.74708221</v>
@@ -15891,7 +15901,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>5310.89473342</v>
@@ -15950,7 +15960,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>5128.95839239</v>
@@ -16009,7 +16019,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>4182.29345126</v>
@@ -16068,7 +16078,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>3457.00171288</v>
@@ -16127,7 +16137,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>2760.06562369</v>
@@ -16186,7 +16196,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>2663.27301001</v>
@@ -16245,7 +16255,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>2888.35593094</v>
@@ -16304,7 +16314,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>2776.62132511</v>
@@ -16363,7 +16373,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>2660.0054315</v>
@@ -16422,7 +16432,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>3618.92757191</v>
@@ -16481,7 +16491,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>3588.91326078</v>
@@ -16540,7 +16550,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>3255.18471978</v>
@@ -16599,7 +16609,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>3665.91725513</v>
@@ -16658,7 +16668,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>3656.23696445</v>
@@ -16717,7 +16727,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>3651.18536619</v>
@@ -16776,7 +16786,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>3601.58288106</v>
@@ -16835,7 +16845,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>3209.19284597</v>
@@ -16894,7 +16904,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>3455.07107901</v>
@@ -16953,7 +16963,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>4402.85408075</v>
@@ -17012,7 +17022,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>4101.00544529</v>
@@ -17071,7 +17081,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>4575.37831366</v>
@@ -17130,7 +17140,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>5151.02501749</v>
@@ -17189,7 +17199,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>5290.50470002</v>
@@ -17248,7 +17258,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>5355.47788923</v>
@@ -17307,7 +17317,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>5336.94397937</v>
@@ -17366,7 +17376,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>4950.86517118</v>
@@ -17425,7 +17435,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>5575.50415512</v>
@@ -17484,7 +17494,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>5388.75539526</v>
@@ -17543,7 +17553,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>4889.20685058</v>
@@ -17602,7 +17612,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>4764.29308642</v>
@@ -17661,7 +17671,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>5641.59316662</v>
@@ -17720,7 +17730,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B257" s="2" t="n">
         <v>5532.90220124</v>
@@ -17779,7 +17789,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B258" s="2" t="n">
         <v>6489.83520009</v>
@@ -17838,7 +17848,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B259" s="2" t="n">
         <v>6704.55025099</v>
@@ -17897,7 +17907,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B260" s="2" t="n">
         <v>6858.54475622</v>
@@ -17956,7 +17966,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B261" s="2" t="n">
         <v>7671.06005752</v>
@@ -18015,7 +18025,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B262" s="2" t="n">
         <v>6888.51334482</v>
@@ -18074,7 +18084,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B263" s="2" t="n">
         <v>6303.01564037</v>
@@ -18133,7 +18143,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B264" s="2" t="n">
         <v>6229.75667786</v>
@@ -18192,7 +18202,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B265" s="2" t="n">
         <v>5987.40447621</v>
@@ -18251,7 +18261,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B266" s="2" t="n">
         <v>5363.7523267</v>
@@ -18310,7 +18320,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B267" s="2" t="n">
         <v>4724.98383984</v>
@@ -18369,7 +18379,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B268" s="2" t="n">
         <v>5146.50963753</v>
@@ -18428,7 +18438,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B269" s="2" t="n">
         <v>4769.81297701</v>
@@ -18487,7 +18497,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B270" s="2" t="n">
         <v>5987.10122764</v>
@@ -18546,7 +18556,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B271" s="2" t="n">
         <v>6033.5045701</v>
@@ -18605,7 +18615,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B272" s="2" t="n">
         <v>6344.87749766</v>
@@ -18664,7 +18674,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B273" s="2" t="n">
         <v>6276.43274486</v>
@@ -18723,7 +18733,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B274" s="2" t="n">
         <v>5854.62747987</v>
@@ -18782,7 +18792,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B275" s="2" t="n">
         <v>6256.61237137</v>
@@ -18841,7 +18851,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B276" s="2" t="n">
         <v>5779.47081789</v>
@@ -18900,7 +18910,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B277" s="2" t="n">
         <v>5436.52903906</v>
@@ -18959,7 +18969,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B278" s="2" t="n">
         <v>5358.22554072</v>
@@ -19018,7 +19028,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B279" s="2" t="n">
         <v>5174.7487146</v>
@@ -19077,7 +19087,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B280" s="2" t="n">
         <v>5619.17967816</v>
@@ -19136,7 +19146,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B281" s="2" t="n">
         <v>6193.45819915</v>
@@ -19195,7 +19205,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B282" s="2" t="n">
         <v>7028.08914824</v>
@@ -19254,7 +19264,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B283" s="2" t="n">
         <v>6642.80578211</v>
@@ -19313,7 +19323,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B284" s="2" t="n">
         <v>6988.15531125</v>
@@ -19372,7 +19382,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B285" s="2" t="n">
         <v>7073.89803118</v>
@@ -19431,7 +19441,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B286" s="2" t="n">
         <v>6028.93204507</v>
@@ -19490,7 +19500,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B287" s="2" t="n">
         <v>6830.95882253</v>
@@ -19549,7 +19559,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B288" s="2" t="n">
         <v>6091.64607397</v>
@@ -19608,7 +19618,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B289" s="2" t="n">
         <v>5411.70274783</v>
@@ -19667,7 +19677,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B290" s="2" t="n">
         <v>5648.62773701</v>
@@ -19726,7 +19736,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B291" s="2" t="n">
         <v>5537.45467736</v>
@@ -19785,7 +19795,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B292" s="2" t="n">
         <v>5389.89160671</v>
@@ -19844,7 +19854,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B293" s="2" t="n">
         <v>5656.13981304</v>
@@ -19903,7 +19913,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B294" s="2" t="n">
         <v>5776.91925095</v>
@@ -19962,7 +19972,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B295" s="2" t="n">
         <v>5847.78330666</v>
@@ -20021,7 +20031,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B296" s="2" t="n">
         <v>6145.08568447</v>
@@ -20080,7 +20090,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B297" s="2" t="n">
         <v>5644.38807483</v>
@@ -20139,7 +20149,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B298" s="2" t="n">
         <v>5644.08801985</v>
@@ -20198,7 +20208,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B299" s="2" t="n">
         <v>5494.2799463</v>
@@ -20257,7 +20267,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B300" s="2" t="n">
         <v>4650.98823493</v>
@@ -20316,7 +20326,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B301" s="2" t="n">
         <v>4300.42248457</v>
@@ -20375,7 +20385,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B302" s="2" t="n">
         <v>4362.70509514</v>
@@ -20434,7 +20444,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B303" s="2" t="n">
         <v>4084.50122666</v>
@@ -20493,7 +20503,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B304" s="2" t="n">
         <v>5058.82116417</v>
@@ -20552,7 +20562,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B305" s="2" t="n">
         <v>4932.94982219</v>
@@ -20611,7 +20621,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B306" s="2" t="n">
         <v>5002.90368466</v>
@@ -20670,7 +20680,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B307" s="2" t="n">
         <v>5707.06641349</v>
@@ -20729,7 +20739,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B308" s="2" t="n">
         <v>5800.57725626</v>
@@ -20788,7 +20798,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B309" s="2" t="n">
         <v>5604.94745843</v>
@@ -20847,7 +20857,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B310" s="2" t="n">
         <v>5487.0890578</v>
@@ -20906,7 +20916,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B311" s="2" t="n">
         <v>5058.00128103</v>
@@ -20965,7 +20975,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B312" s="2" t="n">
         <v>4699.56622909</v>
@@ -21024,7 +21034,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B313" s="2" t="n">
         <v>4403.90684521</v>
@@ -21083,7 +21093,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B314" s="2" t="n">
         <v>4123.27232551</v>
@@ -21142,7 +21152,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B315" s="2" t="n">
         <v>4096.19002125</v>
@@ -21201,7 +21211,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B316" s="2" t="n">
         <v>4556.33606667</v>
@@ -21260,7 +21270,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B317" s="2" t="n">
         <v>4422.65670089</v>
@@ -21319,7 +21329,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B318" s="2" t="n">
         <v>4873.58161759</v>
@@ -21378,7 +21388,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B319" s="2" t="n">
         <v>5046.37328503</v>
@@ -21437,7 +21447,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B320" s="2" t="n">
         <v>4717.63722243</v>
@@ -21496,7 +21506,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B321" s="2" t="n">
         <v>5173.69321917</v>
@@ -21555,7 +21565,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B322" s="2" t="n">
         <v>4741.42728347</v>
@@ -21614,7 +21624,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B323" s="2" t="n">
         <v>4782.95418009</v>
@@ -21673,7 +21683,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B324" s="2" t="n">
         <v>4723.15060522</v>
@@ -21732,7 +21742,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B325" s="2" t="n">
         <v>4594.79292979</v>
@@ -21791,7 +21801,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B326" s="2" t="n">
         <v>4344.1163461</v>
@@ -21850,7 +21860,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B327" s="2" t="n">
         <v>4117.16865957</v>
@@ -21909,7 +21919,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B328" s="2" t="n">
         <v>5474.98330466</v>
@@ -21968,7 +21978,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B329" s="2" t="n">
         <v>4973.10245577</v>
@@ -22027,7 +22037,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B330" s="2" t="n">
         <v>6064.32059245</v>
@@ -22086,7 +22096,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B331" s="2" t="n">
         <v>5898.14821469</v>
@@ -22145,7 +22155,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B332" s="2" t="n">
         <v>6042.73614412</v>
@@ -22204,7 +22214,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B333" s="2" t="n">
         <v>6316.73196131</v>
@@ -22263,7 +22273,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B334" s="2" t="n">
         <v>5968.34766456</v>
@@ -22322,7 +22332,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B335" s="2" t="n">
         <v>6209.13406815</v>
@@ -22381,7 +22391,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B336" s="2" t="n">
         <v>6163.36467863</v>
@@ -22440,7 +22450,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B337" s="2" t="n">
         <v>5365.93059037</v>
@@ -22499,7 +22509,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B338" s="2" t="n">
         <v>5743.26392064</v>
@@ -22558,7 +22568,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B339" s="2" t="n">
         <v>5195.98021667</v>
@@ -22617,7 +22627,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B340" s="2" t="n">
         <v>5978.9496414</v>
@@ -22676,7 +22686,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B341" s="2" t="n">
         <v>6105.58506503</v>
@@ -22735,7 +22745,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B342" s="2" t="n">
         <v>6448.00054965</v>
@@ -22794,7 +22804,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B343" s="2" t="n">
         <v>5461.01935893</v>
@@ -22853,7 +22863,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B344" s="2" t="n">
         <v>6182.40102398</v>
@@ -22912,7 +22922,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B345" s="2" t="n">
         <v>6314.30100303</v>
@@ -22971,7 +22981,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B346" s="2" t="n">
         <v>4699.95462948</v>
@@ -23030,7 +23040,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B347" s="2" t="n">
         <v>5073.4736818</v>
@@ -23089,7 +23099,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B348" s="2" t="n">
         <v>4363.01217956</v>
@@ -23148,7 +23158,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B349" s="2" t="n">
         <v>3916.87314604</v>
@@ -23207,7 +23217,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B350" s="2" t="n">
         <v>4211.80680606</v>
@@ -23266,7 +23276,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B351" s="2" t="n">
         <v>3997.93744612</v>
@@ -23325,7 +23335,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B352" s="2" t="n">
         <v>3956.31273037</v>
@@ -23384,7 +23394,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B353" s="2" t="n">
         <v>4172.28163326</v>
@@ -23443,7 +23453,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B354" s="2" t="n">
         <v>4644.78872143</v>
@@ -23502,7 +23512,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B355" s="2" t="n">
         <v>4171.39180551</v>
@@ -23561,7 +23571,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B356" s="2" t="n">
         <v>4905.29784078</v>
@@ -23620,7 +23630,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B357" s="2" t="n">
         <v>4400.09418116</v>
@@ -23679,7 +23689,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B358" s="2" t="n">
         <v>4001.94180505</v>
@@ -23738,7 +23748,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B359" s="2" t="n">
         <v>4121.43024042</v>
@@ -23797,7 +23807,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B360" s="2" t="n">
         <v>3408.68218244</v>
@@ -23856,7 +23866,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B361" s="2" t="n">
         <v>3133.06458335</v>
@@ -23915,7 +23925,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B362" s="2" t="n">
         <v>3535.43384682</v>
@@ -23974,7 +23984,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B363" s="2" t="n">
         <v>3191.22422754</v>
@@ -24033,7 +24043,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B364" s="2" t="n">
         <v>3154.187947</v>
@@ -24092,7 +24102,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B365" s="2" t="n">
         <v>2894.41933464</v>
@@ -24151,7 +24161,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B366" s="2" t="n">
         <v>3165.9282486</v>
@@ -24210,7 +24220,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B367" s="2" t="n">
         <v>3299.30699887</v>
@@ -24269,7 +24279,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B368" s="2" t="n">
         <v>3450.78954023</v>
@@ -24328,7 +24338,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B369" s="2" t="n">
         <v>3508.21398643</v>
@@ -24387,7 +24397,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B370" s="2" t="n">
         <v>4128.99410758</v>
@@ -24446,7 +24456,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B371" s="2" t="n">
         <v>4004.44094513</v>
@@ -24505,7 +24515,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B372" s="2" t="n">
         <v>4114.75650827</v>
@@ -24564,7 +24574,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B373" s="2" t="n">
         <v>3907.941187</v>
@@ -24623,7 +24633,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B374" s="2" t="n">
         <v>3843.54738808</v>
@@ -24682,7 +24692,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B375" s="2" t="n">
         <v>3712.67659416</v>
@@ -24741,7 +24751,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B376" s="2" t="n">
         <v>5320.17156768</v>
@@ -24800,7 +24810,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B377" s="2" t="n">
         <v>4672.8071307</v>
@@ -24859,7 +24869,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B378" s="2" t="n">
         <v>5141.00165331</v>
@@ -24918,7 +24928,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B379" s="2" t="n">
         <v>5908.78147225</v>
@@ -24977,7 +24987,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B380" s="2" t="n">
         <v>5715.43837769</v>
@@ -25036,7 +25046,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B381" s="2" t="n">
         <v>5753.64398837</v>
@@ -25095,7 +25105,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B382" s="2" t="n">
         <v>5885.68205141</v>
@@ -25154,7 +25164,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B383" s="2" t="n">
         <v>5247.23213626</v>
@@ -25213,7 +25223,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B384" s="2" t="n">
         <v>5767.0360416</v>
@@ -25272,7 +25282,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B385" s="2" t="n">
         <v>6215.73500319</v>
@@ -25331,7 +25341,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B386" s="2" t="n">
         <v>5251.2936057</v>
@@ -25390,7 +25400,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B387" s="2" t="n">
         <v>5638.66689554</v>
@@ -25449,7 +25459,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B388" s="2" t="n">
         <v>7083.88545587</v>
@@ -25508,7 +25518,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B389" s="2" t="n">
         <v>6889.29493355</v>
@@ -25567,7 +25577,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B390" s="2" t="n">
         <v>7891.52548409</v>
@@ -25626,7 +25636,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B391" s="2" t="n">
         <v>8666.66310103</v>
@@ -25685,7 +25695,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B392" s="2" t="n">
         <v>8301.61983506</v>
@@ -25744,7 +25754,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B393" s="2" t="n">
         <v>7917.87095572</v>
@@ -25803,7 +25813,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B394" s="2" t="n">
         <v>7143.96142178</v>
@@ -25862,7 +25872,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B395" s="2" t="n">
         <v>6088.90578233</v>
@@ -25921,7 +25931,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B396" s="2" t="n">
         <v>5778.03041075</v>
@@ -25980,7 +25990,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B397" s="2" t="n">
         <v>5088.65847728</v>
@@ -26039,7 +26049,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B398" s="2" t="n">
         <v>5366.60710713</v>
@@ -26098,7 +26108,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B399" s="2" t="n">
         <v>5031.00287783</v>
@@ -26157,7 +26167,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B400" s="2" t="n">
         <v>6843.81462087</v>
@@ -26216,7 +26226,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B401" s="2" t="n">
         <v>6110.21482628</v>
@@ -26275,7 +26285,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B402" s="2" t="n">
         <v>7406.21448106</v>
@@ -26334,7 +26344,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B403" s="2" t="n">
         <v>7252.0259066</v>
@@ -26393,7 +26403,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B404" s="2" t="n">
         <v>6758.36357653</v>
@@ -26452,7 +26462,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B405" s="2" t="n">
         <v>6898.73533827</v>
@@ -26511,7 +26521,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B406" s="2" t="n">
         <v>6520.37702434</v>
@@ -26570,7 +26580,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B407" s="2" t="n">
         <v>5849.30135642</v>
@@ -26629,7 +26639,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B408" s="2" t="n">
         <v>5517.43704224</v>
@@ -26688,7 +26698,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B409" s="2" t="n">
         <v>4271.86806454</v>
@@ -26747,7 +26757,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B410" s="2" t="n">
         <v>4603.95464722</v>
@@ -26806,7 +26816,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B411" s="2" t="n">
         <v>4118.05743199</v>
@@ -26865,7 +26875,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B412" s="2" t="n">
         <v>4331.57077283</v>
@@ -26924,7 +26934,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B413" s="2" t="n">
         <v>4704.52137908</v>
@@ -26983,7 +26993,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B414" s="2" t="n">
         <v>5012.11741383</v>
@@ -27042,7 +27052,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B415" s="2" t="n">
         <v>4687.44850467</v>
@@ -27101,7 +27111,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B416" s="2" t="n">
         <v>5727.05446816</v>
@@ -27160,7 +27170,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B417" s="2" t="n">
         <v>4882.94094487</v>
@@ -27219,7 +27229,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B418" s="2" t="n">
         <v>5970.95870549</v>
@@ -27278,7 +27288,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B419" s="2" t="n">
         <v>6120.46379453</v>
@@ -27337,7 +27347,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B420" s="2" t="n">
         <v>5249.07209284</v>
@@ -27396,7 +27406,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B421" s="2" t="n">
         <v>5367.41141389</v>
@@ -27455,7 +27465,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B422" s="2" t="n">
         <v>5752.75016151</v>
@@ -27514,7 +27524,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B423" s="2" t="n">
         <v>5864.28756064</v>
@@ -27573,7 +27583,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B424" s="2" t="n">
         <v>6018.84797559</v>
@@ -27632,7 +27642,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>6459.95918914</v>
@@ -27691,7 +27701,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>6487.97000892</v>
@@ -27750,7 +27760,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B427" s="2" t="n">
         <v>6395.91011981</v>
@@ -27809,7 +27819,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B428" s="2" t="n">
         <v>6853.67165011</v>
@@ -27868,7 +27878,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B429" s="2" t="n">
         <v>6462.72070149</v>
@@ -27927,7 +27937,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B430" s="2" t="n">
         <v>7191.13346186</v>
@@ -27986,7 +27996,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B431" s="2" t="n">
         <v>7149.97099752</v>
@@ -28045,7 +28055,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B432" s="2" t="n">
         <v>5597.99248129</v>
@@ -28104,7 +28114,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B433" s="2" t="n">
         <v>5555.90492346</v>
@@ -28163,7 +28173,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>5056.67015725</v>
@@ -28222,7 +28232,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>5166.57388213</v>
@@ -28281,7 +28291,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>6115.8952783</v>
@@ -28340,7 +28350,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B437" s="2" t="n">
         <v>6203.53666768</v>
@@ -28399,7 +28409,7 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B438" s="2"/>
       <c r="C438" s="3" t="n">
@@ -28432,7 +28442,7 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B439" s="2"/>
       <c r="C439" s="3" t="n">
@@ -28465,7 +28475,7 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B440" s="2"/>
       <c r="C440" s="3" t="n">
@@ -28498,7 +28508,7 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B441" s="2"/>
       <c r="C441" s="3" t="n">
@@ -28531,7 +28541,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B442" s="2"/>
       <c r="C442" s="3" t="n">
@@ -28564,7 +28574,7 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B443" s="2"/>
       <c r="C443" s="3" t="n">
@@ -28597,7 +28607,7 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B444" s="2"/>
       <c r="C444" s="3" t="n">
@@ -28630,7 +28640,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B445" s="2"/>
       <c r="C445" s="3" t="n">
@@ -28663,7 +28673,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B446" s="2"/>
       <c r="C446" s="3" t="n">
@@ -28696,7 +28706,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B447" s="2"/>
       <c r="C447" s="3" t="n">
@@ -28729,7 +28739,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B448" s="2"/>
       <c r="C448" s="3" t="n">
@@ -28762,7 +28772,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B449" s="2"/>
       <c r="C449" s="3" t="n">
@@ -28795,7 +28805,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B450" s="2"/>
       <c r="C450" s="3"/>
@@ -28818,7 +28828,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B451" s="2"/>
       <c r="C451" s="3"/>
@@ -28841,7 +28851,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B452" s="2"/>
       <c r="C452" s="3"/>
@@ -28864,7 +28874,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B453" s="2"/>
       <c r="C453" s="3"/>
@@ -28887,7 +28897,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B454" s="2"/>
       <c r="C454" s="3"/>
@@ -28910,7 +28920,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B455" s="2"/>
       <c r="C455" s="3"/>
@@ -28933,7 +28943,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B456" s="2"/>
       <c r="C456" s="3"/>
@@ -28956,7 +28966,7 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B457" s="2"/>
       <c r="C457" s="3"/>
@@ -28979,7 +28989,7 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B458" s="2"/>
       <c r="C458" s="3"/>
@@ -29002,7 +29012,7 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B459" s="2"/>
       <c r="C459" s="3"/>
@@ -29025,7 +29035,7 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B460" s="2"/>
       <c r="C460" s="3"/>
@@ -29048,7 +29058,7 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B461" s="2"/>
       <c r="C461" s="3"/>
@@ -29071,7 +29081,7 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B462" s="2"/>
       <c r="C462" s="3"/>
@@ -29094,7 +29104,7 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B463" s="2"/>
       <c r="C463" s="3"/>
@@ -29117,7 +29127,7 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B464" s="2"/>
       <c r="C464" s="3"/>
@@ -29140,7 +29150,7 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B465" s="2"/>
       <c r="C465" s="3"/>
@@ -29163,7 +29173,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B466" s="2"/>
       <c r="C466" s="3"/>
@@ -29186,7 +29196,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B467" s="2"/>
       <c r="C467" s="3"/>
@@ -29209,7 +29219,7 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B468" s="2"/>
       <c r="C468" s="3"/>
@@ -29232,7 +29242,7 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B469" s="2"/>
       <c r="C469" s="3"/>
@@ -29255,7 +29265,7 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B470" s="2"/>
       <c r="C470" s="3"/>
@@ -29278,7 +29288,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B471" s="2"/>
       <c r="C471" s="3"/>
@@ -29301,7 +29311,7 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B472" s="2"/>
       <c r="C472" s="3"/>
@@ -29324,7 +29334,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B473" s="2"/>
       <c r="C473" s="3"/>
@@ -29347,7 +29357,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B474" s="2"/>
       <c r="C474" s="3"/>
@@ -29370,7 +29380,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B475" s="2"/>
       <c r="C475" s="3"/>
@@ -29393,7 +29403,7 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B476" s="2"/>
       <c r="C476" s="3"/>
@@ -29416,7 +29426,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B477" s="2"/>
       <c r="C477" s="3"/>
@@ -29439,7 +29449,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B478" s="2"/>
       <c r="C478" s="3"/>
@@ -29462,7 +29472,7 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B479" s="2"/>
       <c r="C479" s="3"/>
@@ -29485,7 +29495,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B480" s="2"/>
       <c r="C480" s="3"/>
@@ -29508,7 +29518,7 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B481" s="2"/>
       <c r="C481" s="3"/>
@@ -29531,7 +29541,7 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B482" s="2"/>
       <c r="C482" s="3"/>
@@ -29554,7 +29564,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B483" s="2"/>
       <c r="C483" s="3"/>
@@ -29577,7 +29587,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B484" s="2"/>
       <c r="C484" s="3"/>
@@ -29600,7 +29610,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B485" s="2"/>
       <c r="C485" s="3"/>
@@ -29623,7 +29633,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B486" s="2"/>
       <c r="C486" s="3"/>
@@ -29646,7 +29656,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B487" s="2"/>
       <c r="C487" s="3"/>
@@ -29669,7 +29679,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B488" s="2"/>
       <c r="C488" s="3"/>
@@ -29692,7 +29702,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B489" s="2"/>
       <c r="C489" s="3"/>
@@ -29715,7 +29725,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B490" s="2"/>
       <c r="C490" s="3"/>
@@ -29738,7 +29748,7 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B491" s="2"/>
       <c r="C491" s="3"/>
@@ -29761,7 +29771,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B492" s="2"/>
       <c r="C492" s="3"/>
@@ -29784,7 +29794,7 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B493" s="2"/>
       <c r="C493" s="3"/>
@@ -29818,97 +29828,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -29932,7 +29942,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -29942,160 +29952,160 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0886635792378331</v>
+        <v>0.0906995419836073</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.162886150413617</v>
+        <v>0.165271692650723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.264128872120278</v>
+        <v>0.26444061524679</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.366216641970874</v>
+        <v>0.363342131531332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.449977585105896</v>
+        <v>0.446233016972755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.504146673384343</v>
+        <v>0.500956195342829</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.542625487264087</v>
+        <v>0.540929572813878</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.585799644124998</v>
+        <v>0.586380770999901</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.624444064170084</v>
+        <v>0.62563183132025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.65041050209782</v>
+        <v>0.65166497545345</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.672850464658403</v>
+        <v>0.674660126747741</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.642891020153625</v>
+        <v>0.644826460289047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.550962636830195</v>
+        <v>0.552763566371641</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.434560479531333</v>
+        <v>0.436238769432226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.31162423327473</v>
+        <v>0.313432852746091</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.208887641113562</v>
+        <v>0.211291952418927</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.13049861294805</v>
+        <v>0.132736274492503</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.0555499359158826</v>
+        <v>0.0564422687776475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>-0.00220882531434005</v>
+        <v>-0.00272006084188716</v>
       </c>
     </row>
     <row r="24">
